--- a/audio_ficition/books/excel/book-zh-bilibili.xlsx
+++ b/audio_ficition/books/excel/book-zh-bilibili.xlsx
@@ -452,9 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-07-05 16:07:33</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -463,9 +467,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025-07-06 16:07:33</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -474,9 +482,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2025-07-07 16:07:33</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -485,9 +497,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2025-07-08 16:07:33</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -496,9 +512,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2025-07-09 16:07:33</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -507,9 +527,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2025-07-10 16:07:33</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -518,9 +542,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-07-11 16:07:33</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -529,9 +557,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025-07-12 16:07:33</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -540,9 +572,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-07-13 16:07:33</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -551,9 +587,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-07-14 16:07:33</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -562,9 +602,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-07-15 16:07:33</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -573,9 +617,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-07-16 16:07:33</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -584,9 +632,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025-07-17 16:07:33</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -595,9 +647,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025-07-18 16:07:33</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">

--- a/audio_ficition/books/excel/book-zh-bilibili.xlsx
+++ b/audio_ficition/books/excel/book-zh-bilibili.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24ae0e5d-9b52-4494-9455-35b19fc44049</t>
+          <t>1bc12a48-36e1-4db2-8ea0-01237920b32e</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -471,14 +471,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-07-06 16:07:33</t>
+          <t>2025-07-24 16:07:33</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2ceb92c5-c928-45d8-b890-5ae9e03b5119</t>
+          <t>1da05845-ad59-4bde-9c80-6566ced74d1d</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -486,14 +486,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-07-07 16:07:33</t>
+          <t>2025-07-25 16:07:33</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>350bb7ab-0470-49e1-97be-d95fff3044f7</t>
+          <t>24ae0e5d-9b52-4494-9455-35b19fc44049</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -501,14 +501,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-07-08 16:07:33</t>
+          <t>2025-07-06 16:07:33</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3ed6ef2d-7f63-4da1-acb9-901796b60b74</t>
+          <t>2ceb92c5-c928-45d8-b890-5ae9e03b5119</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -516,14 +516,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-07-09 16:07:33</t>
+          <t>2025-07-07 16:07:33</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5f23927e-e500-4804-8a00-b70a6cd65ec6</t>
+          <t>3032119d-bbf6-4fd5-bd9d-8cb84866f0c4</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -531,14 +531,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-07-10 16:07:33</t>
+          <t>2025-07-26 16:07:33</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>724c832c-bc78-429d-8fc5-04aa83db9c89</t>
+          <t>350bb7ab-0470-49e1-97be-d95fff3044f7</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -546,14 +546,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-07-11 16:07:33</t>
+          <t>2025-07-08 16:07:33</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>736522cc-f32d-4c0f-9c9d-d2c4ef6b1476</t>
+          <t>3788599b-76ed-42f8-9383-10741650715d</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -561,14 +561,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-07-12 16:07:33</t>
+          <t>2025-07-27 16:07:33</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9c56784e-28e3-4741-915c-18d120ef456d</t>
+          <t>3ed6ef2d-7f63-4da1-acb9-901796b60b74</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -576,14 +576,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025-07-13 16:07:33</t>
+          <t>2025-07-09 16:07:33</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9e796dbe-a250-4d32-9625-567cb2eb38f3</t>
+          <t>40c050dd-583b-4c80-8441-e7f579f839c6</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -591,74 +591,58 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025-07-14 16:07:33</t>
+          <t>2025-07-28 16:07:33</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>b6946244-69fe-4d47-bed0-4147f57c461b</t>
+          <t>42593df4-dd63-4365-b854-1368c357e675</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2025-07-15 16:07:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>b8dc8a08-9fc5-45e9-9ed8-d8697cc55bf6</t>
+          <t>45113314-015a-4fdf-b5b2-62c2426e646c</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2025-07-16 16:07:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bc3fc3f9-4746-49f3-a714-efc43d1799e0</t>
+          <t>4695d2a0-29b0-4cdf-bbc4-e30e20d30068</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2025-07-17 16:07:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>d6aa432f-76ee-45b1-be1e-a39a0f14a114</t>
+          <t>52b8dea9-36f2-4e11-ac9f-6fdb0f5cc178</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2025-07-18 16:07:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dbb30461-a314-4850-9b22-f6c7a599cd35</t>
+          <t>56bf073c-9aa5-43d2-866e-e32fdfe886b7</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -669,18 +653,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dbe55589-7481-4587-9ba7-abfde7734b30</t>
+          <t>5f23927e-e500-4804-8a00-b70a6cd65ec6</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025-07-10 16:07:33</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ef9c920f-c6a4-45b4-bede-87ddc2de01f9</t>
+          <t>630c2762-a1ff-4284-acf6-268826bb2445</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -691,24 +679,285 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>f230cdb7-6c39-491e-bb5e-f2a695fff5b5</t>
+          <t>724c832c-bc78-429d-8fc5-04aa83db9c89</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025-07-11 16:07:33</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>736522cc-f32d-4c0f-9c9d-d2c4ef6b1476</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025-07-12 16:07:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>765624b6-3c00-40c6-aa33-93d8a30dd1b6</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>77905a02-a273-4efa-932d-c9fb3f396c22</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>83a7e370-b35f-4a56-9c35-d5f6e25479fb</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>8aafe530-6c68-4c6e-a757-3255ee05bd04</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>9c56784e-28e3-4741-915c-18d120ef456d</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025-07-13 16:07:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>9e796dbe-a250-4d32-9625-567cb2eb38f3</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2025-07-14 16:07:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>aef4cd17-5e74-4fc2-bddb-8ac8296af0ef</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>b6946244-69fe-4d47-bed0-4147f57c461b</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2025-07-15 16:07:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>b8dc8a08-9fc5-45e9-9ed8-d8697cc55bf6</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2025-07-16 16:07:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>bc3fc3f9-4746-49f3-a714-efc43d1799e0</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2025-07-17 16:07:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>bcef560f-2230-44fe-b20f-5ff89ae62785</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>d2b8eae4-2e78-4136-82ce-7742dfe13aa0</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>d6aa432f-76ee-45b1-be1e-a39a0f14a114</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2025-07-18 16:07:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dbb30461-a314-4850-9b22-f6c7a599cd35</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2025-07-19 16:07:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>dbe55589-7481-4587-9ba7-abfde7734b30</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2025-07-20 16:07:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>e9b94bb7-43ba-4f6a-9f59-e1d3d8e763a3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ef9c920f-c6a4-45b4-bede-87ddc2de01f9</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2025-07-21 16:07:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>f230cdb7-6c39-491e-bb5e-f2a695fff5b5</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2025-07-22 16:07:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>f5a9a5e9-a204-41ee-994e-f1b067d95ddf</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2025-07-23 16:07:33</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
